--- a/data/trans_dic/IP16A98-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A98-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido otros medicamentos</t>
+          <t>Menores que han  consumido otros medicamentos (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 23,95</t>
+          <t>2,75; 27,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 34,14</t>
+          <t>4,0; 32,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,06; 38,67</t>
+          <t>10,92; 37,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,39</t>
+          <t>3,04; 22,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 37,03</t>
+          <t>4,05; 36,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 24,81</t>
+          <t>1,84; 25,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,39; 18,79</t>
+          <t>4,54; 19,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,32; 26,68</t>
+          <t>7,46; 27,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,43; 26,0</t>
+          <t>7,73; 26,18</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,24</t>
+          <t>0,0; 19,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,2; 40,68</t>
+          <t>5,37; 40,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,61</t>
+          <t>0,0; 15,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,67; 47,55</t>
+          <t>5,67; 47,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 28,85</t>
+          <t>3,4; 30,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,07; 26,07</t>
+          <t>2,0; 24,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,64; 23,56</t>
+          <t>5,74; 24,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,43; 27,59</t>
+          <t>6,47; 27,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 14,75</t>
+          <t>2,81; 15,83</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,08</t>
+          <t>0,0; 34,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,42; 53,25</t>
+          <t>6,34; 49,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,15</t>
+          <t>0,0; 35,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,59</t>
+          <t>0,0; 34,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,86; 47,14</t>
+          <t>5,73; 47,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,18; 56,24</t>
+          <t>12,86; 55,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,14; 26,56</t>
+          <t>2,92; 24,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,63; 38,83</t>
+          <t>7,93; 38,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,19; 42,06</t>
+          <t>10,93; 41,27</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,67; 23,42</t>
+          <t>6,91; 22,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,7; 28,89</t>
+          <t>10,13; 30,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 38,96</t>
+          <t>4,2; 37,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,64; 28,21</t>
+          <t>10,69; 28,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,2; 33,97</t>
+          <t>12,41; 34,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,65; 44,91</t>
+          <t>16,2; 47,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,61; 22,77</t>
+          <t>10,65; 22,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,27; 27,1</t>
+          <t>13,23; 27,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,79; 32,98</t>
+          <t>9,29; 33,49</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,83; 28,74</t>
+          <t>5,86; 27,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,0; 33,65</t>
+          <t>8,61; 35,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,44; 38,11</t>
+          <t>11,03; 36,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,79; 28,58</t>
+          <t>4,78; 27,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,59; 39,78</t>
+          <t>12,98; 41,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,43; 23,96</t>
+          <t>5,79; 24,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,51; 22,95</t>
+          <t>7,37; 22,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,05; 32,13</t>
+          <t>13,57; 33,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,82; 25,65</t>
+          <t>10,47; 26,39</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,23</t>
+          <t>0,0; 58,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,24</t>
+          <t>0,0; 27,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,26; 64,35</t>
+          <t>20,09; 65,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,38; 44,23</t>
+          <t>5,06; 45,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,52; 51,57</t>
+          <t>6,67; 51,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,72; 54,43</t>
+          <t>10,78; 55,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,7; 36,01</t>
+          <t>6,48; 36,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,49; 32,29</t>
+          <t>5,79; 30,23</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19,53; 50,01</t>
+          <t>20,19; 52,46</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,86; 17,04</t>
+          <t>8,32; 17,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,34; 23,49</t>
+          <t>12,07; 23,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,17; 28,21</t>
+          <t>10,15; 27,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,3; 21,6</t>
+          <t>10,97; 21,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,28; 26,07</t>
+          <t>13,98; 25,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,72; 26,48</t>
+          <t>13,23; 25,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,93; 17,66</t>
+          <t>10,95; 17,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,72; 22,5</t>
+          <t>14,69; 23,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,29; 24,09</t>
+          <t>13,49; 23,84</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han  consumido otros medicamentos (tasa de respuesta: 99,14%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2402</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5540</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2909</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2630</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4002</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>8170</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>574; 5706</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>633; 5149</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2715; 9415</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>644; 4842</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>719; 6471</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>579; 8102</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1913; 8303</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2506; 9343</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>4348; 14727</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1369</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2804</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2199</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2098</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4173</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4239</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>3285</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4286</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>645; 4850</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3638</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>686; 5792</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>649; 5865</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>470; 5663</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1936; 8097</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2008; 8394</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1320; 7427</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1931</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2036</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5303</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2652</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3967</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>6411</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3497</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>561; 4366</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3452</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4272</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>589; 4860</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2225; 9644</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>664; 5612</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1516; 7271</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2940; 11099</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>6632</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8452</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11965</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10389</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>7419</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>14625</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>17021</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>15871</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>26590</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3363; 10931</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>4707; 14090</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>3211; 28950</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>6091; 16188</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>4283; 11761</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>9048; 26673</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>11243; 23477</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>10714; 22530</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>12280; 44277</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>4226</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5072</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6627</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3389</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>6245</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>4619</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>7615</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>11317</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>11246</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1678; 7934</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2293; 9455</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3188; 10583</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1277; 7412</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3331; 10604</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2082; 8673</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>4079; 12705</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>7096; 17764</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>6796; 17123</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1206</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5038</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2679</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2234</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>4241</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>4018</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>3440</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>9279</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4119</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3642</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2455; 7959</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>699; 6209</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>653; 5076</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1649; 8438</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>1352; 7636</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>1319; 6894</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>5555; 14436</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>16864</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>21104</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>31464</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>22618</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>23042</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>33516</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>39482</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>44145</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>64980</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>11413; 23887</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>14826; 28895</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>17806; 47558</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>15718; 30686</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>16367; 30162</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>23721; 46297</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>30698; 50108</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>35241; 55175</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>47848; 84570</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A98-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A98-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,75; 27,28</t>
+          <t>2,74; 23,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,0; 32,5</t>
+          <t>3,67; 32,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,92; 37,88</t>
+          <t>11,48; 38,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 22,84</t>
+          <t>2,99; 23,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,05; 36,47</t>
+          <t>4,01; 36,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 25,8</t>
+          <t>1,88; 26,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,54; 19,71</t>
+          <t>3,22; 19,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,46; 27,82</t>
+          <t>7,47; 29,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,73; 26,18</t>
+          <t>7,53; 25,58</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,79</t>
+          <t>0,0; 19,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,37; 40,43</t>
+          <t>5,26; 41,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,52</t>
+          <t>0,0; 15,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,67; 47,92</t>
+          <t>5,71; 49,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 30,77</t>
+          <t>3,42; 31,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 24,1</t>
+          <t>3,08; 24,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,74; 24,0</t>
+          <t>4,19; 24,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,47; 27,03</t>
+          <t>5,17; 26,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 15,83</t>
+          <t>2,86; 14,87</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,03</t>
+          <t>0,0; 37,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,34; 49,36</t>
+          <t>6,35; 50,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,97</t>
+          <t>0,0; 37,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,24</t>
+          <t>0,0; 34,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,73; 47,33</t>
+          <t>6,04; 46,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,86; 55,76</t>
+          <t>13,79; 55,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,92; 24,66</t>
+          <t>3,17; 25,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,93; 38,04</t>
+          <t>9,48; 39,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,93; 41,27</t>
+          <t>10,99; 40,61</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,91; 22,47</t>
+          <t>7,69; 23,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,13; 30,31</t>
+          <t>10,82; 28,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,2; 37,9</t>
+          <t>3,52; 37,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,69; 28,41</t>
+          <t>10,68; 28,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,41; 34,07</t>
+          <t>12,5; 36,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,2; 47,76</t>
+          <t>15,42; 43,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,65; 22,23</t>
+          <t>10,68; 22,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,23; 27,81</t>
+          <t>13,54; 27,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,29; 33,49</t>
+          <t>9,0; 34,43</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,86; 27,7</t>
+          <t>5,14; 28,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,61; 35,52</t>
+          <t>8,55; 33,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,03; 36,61</t>
+          <t>11,84; 38,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,78; 27,73</t>
+          <t>4,72; 25,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,98; 41,32</t>
+          <t>12,83; 41,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,79; 24,11</t>
+          <t>4,94; 23,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 22,94</t>
+          <t>7,45; 23,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,57; 33,98</t>
+          <t>13,48; 32,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,47; 26,39</t>
+          <t>10,28; 26,01</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,38</t>
+          <t>0,0; 57,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,96</t>
+          <t>0,0; 29,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,09; 65,12</t>
+          <t>20,77; 64,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,06; 45,01</t>
+          <t>5,02; 43,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,67; 51,91</t>
+          <t>6,68; 51,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,78; 55,15</t>
+          <t>9,22; 51,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,48; 36,62</t>
+          <t>9,11; 39,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,79; 30,23</t>
+          <t>5,29; 31,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,19; 52,46</t>
+          <t>20,06; 51,3</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,32; 17,41</t>
+          <t>8,4; 17,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,07; 23,53</t>
+          <t>12,3; 22,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,15; 27,12</t>
+          <t>10,61; 27,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,97; 21,42</t>
+          <t>11,49; 21,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,98; 25,77</t>
+          <t>13,52; 25,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,23; 25,82</t>
+          <t>13,76; 26,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,95; 17,87</t>
+          <t>10,7; 17,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,69; 23,0</t>
+          <t>14,63; 22,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,49; 23,84</t>
+          <t>13,57; 24,06</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>574; 5706</t>
+          <t>574; 4987</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>633; 5149</t>
+          <t>581; 5200</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2715; 9415</t>
+          <t>2852; 9544</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>644; 4842</t>
+          <t>634; 4999</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>719; 6471</t>
+          <t>712; 6542</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>579; 8102</t>
+          <t>590; 8286</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1913; 8303</t>
+          <t>1355; 8056</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2506; 9343</t>
+          <t>2508; 9864</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4348; 14727</t>
+          <t>4234; 14392</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4286</t>
+          <t>0; 4249</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>645; 4850</t>
+          <t>631; 5034</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3638</t>
+          <t>0; 3710</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>686; 5792</t>
+          <t>690; 6010</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>649; 5865</t>
+          <t>653; 6058</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>470; 5663</t>
+          <t>724; 5650</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1936; 8097</t>
+          <t>1413; 8188</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2008; 8394</t>
+          <t>1604; 8380</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1320; 7427</t>
+          <t>1343; 6978</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3497</t>
+          <t>0; 3804</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>561; 4366</t>
+          <t>561; 4427</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3452</t>
+          <t>0; 3560</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4272</t>
+          <t>0; 4271</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>589; 4860</t>
+          <t>620; 4735</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2225; 9644</t>
+          <t>2385; 9513</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>664; 5612</t>
+          <t>721; 5907</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1516; 7271</t>
+          <t>1812; 7498</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2940; 11099</t>
+          <t>2956; 10922</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3363; 10931</t>
+          <t>3742; 11405</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4707; 14090</t>
+          <t>5032; 13419</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3211; 28950</t>
+          <t>2689; 28765</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6091; 16188</t>
+          <t>6085; 16249</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4283; 11761</t>
+          <t>4315; 12436</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9048; 26673</t>
+          <t>8609; 24494</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11243; 23477</t>
+          <t>11282; 24222</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10714; 22530</t>
+          <t>10969; 22563</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12280; 44277</t>
+          <t>11901; 45530</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1678; 7934</t>
+          <t>1472; 8057</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2293; 9455</t>
+          <t>2275; 8934</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3188; 10583</t>
+          <t>3423; 11024</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1277; 7412</t>
+          <t>1262; 6904</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3331; 10604</t>
+          <t>3293; 10640</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2082; 8673</t>
+          <t>1777; 8549</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4079; 12705</t>
+          <t>4127; 12842</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7096; 17764</t>
+          <t>7048; 17109</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6796; 17123</t>
+          <t>6670; 16879</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4119</t>
+          <t>0; 4065</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3642</t>
+          <t>0; 3865</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2455; 7959</t>
+          <t>2538; 7941</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>699; 6209</t>
+          <t>692; 5990</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>653; 5076</t>
+          <t>653; 5040</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1649; 8438</t>
+          <t>1410; 7872</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1352; 7636</t>
+          <t>1900; 8227</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1319; 6894</t>
+          <t>1206; 7109</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5555; 14436</t>
+          <t>5520; 14118</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11413; 23887</t>
+          <t>11519; 24149</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>14826; 28895</t>
+          <t>15108; 28145</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17806; 47558</t>
+          <t>18614; 47558</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15718; 30686</t>
+          <t>16456; 31428</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>16367; 30162</t>
+          <t>15819; 30417</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23721; 46297</t>
+          <t>24664; 48262</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30698; 50108</t>
+          <t>30011; 49638</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>35241; 55175</t>
+          <t>35094; 54222</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>47848; 84570</t>
+          <t>48145; 85329</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A98-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A98-Clase-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido otros medicamentos (tasa de respuesta: 99,14%)</t>
+          <t>Menores que consumieron otros medicamentos (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9,47%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16,4%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9,08%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>9,53%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>15,16%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>22,29%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9,47%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>16,4%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>15,2%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 23,84</t>
+          <t>0,0; 22,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 32,82</t>
+          <t>3,92; 37,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,48; 38,4</t>
+          <t>1,1; 27,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,99; 23,58</t>
+          <t>2,65; 23,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,01; 36,87</t>
+          <t>3,84; 34,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 26,39</t>
+          <t>10,85; 38,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,22; 19,13</t>
+          <t>3,39; 18,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,47; 29,37</t>
+          <t>7,32; 26,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,53; 25,58</t>
+          <t>8,59; 27,04</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>23,2%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11,54%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8,23%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>6,32%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>17,01%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>23,2%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>11,54%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,62</t>
+          <t>5,67; 47,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,26; 41,96</t>
+          <t>3,4; 28,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,83</t>
+          <t>2,45; 25,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,71; 49,72</t>
+          <t>0,0; 19,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,42; 31,78</t>
+          <t>5,2; 40,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,08; 24,05</t>
+          <t>0,0; 17,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 24,26</t>
+          <t>5,64; 23,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,17; 26,98</t>
+          <t>6,43; 27,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 14,87</t>
+          <t>2,17; 14,58</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10,8%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19,83%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>30,34%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>12,7%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>21,83%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11,54%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10,8%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19,83%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,02%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,02</t>
+          <t>0,0; 33,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,35; 50,04</t>
+          <t>5,86; 47,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,09</t>
+          <t>12,6; 55,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,23</t>
+          <t>0,0; 38,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,04; 46,12</t>
+          <t>6,42; 53,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,79; 55,0</t>
+          <t>0,0; 38,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 25,96</t>
+          <t>3,14; 26,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,48; 39,23</t>
+          <t>7,63; 38,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,99; 40,61</t>
+          <t>10,51; 41,42</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18,24%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21,49%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>27,64%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>13,63%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>18,18%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>15,67%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18,24%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>21,49%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,69; 23,45</t>
+          <t>10,64; 28,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,82; 28,87</t>
+          <t>11,2; 33,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 37,66</t>
+          <t>16,58; 48,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,68; 28,52</t>
+          <t>6,67; 23,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,5; 36,02</t>
+          <t>9,7; 28,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,42; 43,86</t>
+          <t>9,93; 30,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,68; 22,93</t>
+          <t>10,61; 22,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,54; 27,85</t>
+          <t>13,27; 27,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,0; 34,43</t>
+          <t>14,89; 35,67</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12,68%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>24,34%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12,48%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>14,75%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>19,05%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>22,93%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>12,68%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>24,34%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 28,13</t>
+          <t>4,79; 28,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,55; 33,56</t>
+          <t>12,59; 39,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,84; 38,14</t>
+          <t>5,36; 24,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,72; 25,83</t>
+          <t>6,83; 28,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,83; 41,46</t>
+          <t>9,0; 33,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,94; 23,76</t>
+          <t>11,66; 37,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,45; 23,19</t>
+          <t>7,51; 22,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,48; 32,72</t>
+          <t>13,05; 32,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,28; 26,01</t>
+          <t>10,25; 25,44</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>19,42%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>22,84%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>24,72%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>18,98%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>9,26%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>41,22%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>19,42%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>22,84%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>32,42%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,61</t>
+          <t>5,38; 44,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,67</t>
+          <t>6,52; 51,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,77; 64,98</t>
+          <t>8,77; 50,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,02; 43,42</t>
+          <t>0,0; 58,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,68; 51,55</t>
+          <t>0,0; 29,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,22; 51,46</t>
+          <t>20,77; 63,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,11; 39,46</t>
+          <t>6,7; 36,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,29; 31,18</t>
+          <t>5,49; 32,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,06; 51,3</t>
+          <t>18,53; 48,31</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>15,79%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>19,69%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18,64%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>12,29%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>17,18%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>17,94%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15,79%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>19,69%</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,4; 17,6</t>
+          <t>11,3; 21,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,3; 22,92</t>
+          <t>14,28; 26,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,61; 27,12</t>
+          <t>13,69; 27,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,49; 21,94</t>
+          <t>7,86; 17,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,52; 25,99</t>
+          <t>12,34; 23,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,76; 26,92</t>
+          <t>13,64; 24,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,7; 17,7</t>
+          <t>10,93; 17,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,63; 22,61</t>
+          <t>14,72; 22,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,57; 24,06</t>
+          <t>15,13; 24,01</t>
         </is>
       </c>
     </row>
@@ -1432,20 +1432,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido otros medicamentos (tasa de respuesta: 99,14%)</t>
+          <t>Menores que consumieron otros medicamentos (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1543,22 +1543,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2909</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2619</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>1994</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>2402</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5540</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2909</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>5509</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>8128</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>574; 4987</t>
+          <t>0; 4747</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>581; 5200</t>
+          <t>695; 6571</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2852; 9544</t>
+          <t>318; 7830</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634; 4999</t>
+          <t>554; 5010</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>712; 6542</t>
+          <t>609; 5409</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>590; 8286</t>
+          <t>2672; 9545</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1355; 8056</t>
+          <t>1429; 7914</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2508; 9864</t>
+          <t>2460; 8962</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4234; 14392</t>
+          <t>4592; 14458</t>
         </is>
       </c>
     </row>
@@ -1696,32 +1696,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1749,32 +1749,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2804</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2199</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1862</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1369</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2040</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1187</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2804</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2199</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>3032</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4249</t>
+          <t>686; 5748</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>631; 5034</t>
+          <t>648; 5500</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3710</t>
+          <t>555; 5660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>690; 6010</t>
+          <t>0; 4167</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>653; 6058</t>
+          <t>624; 4880</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>724; 5650</t>
+          <t>0; 4048</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1413; 8188</t>
+          <t>1903; 7951</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1604; 8380</t>
+          <t>1996; 8570</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1343; 6978</t>
+          <t>989; 6649</t>
         </is>
       </c>
     </row>
@@ -1869,22 +1869,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1912,32 +1912,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2036</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4558</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>1305</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1931</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1107</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1347</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2036</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5303</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>5650</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3804</t>
+          <t>0; 4191</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>561; 4427</t>
+          <t>601; 4840</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3560</t>
+          <t>1894; 8411</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4271</t>
+          <t>0; 3914</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>620; 4735</t>
+          <t>568; 4710</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2385; 9513</t>
+          <t>0; 3712</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>721; 5907</t>
+          <t>715; 6043</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1812; 7498</t>
+          <t>1458; 7422</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2956; 10922</t>
+          <t>2581; 10167</t>
         </is>
       </c>
     </row>
@@ -2022,32 +2022,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>10389</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7419</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13750</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>6632</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>8452</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>11965</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10389</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7419</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14625</t>
+          <t>7410</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>26590</t>
+          <t>21160</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3742; 11405</t>
+          <t>6061; 16070</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5032; 13419</t>
+          <t>3866; 11729</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2689; 28765</t>
+          <t>8246; 23957</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6085; 16249</t>
+          <t>3244; 11393</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4315; 12436</t>
+          <t>4510; 13431</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8609; 24494</t>
+          <t>4224; 12888</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11282; 24222</t>
+          <t>11207; 24053</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10969; 22563</t>
+          <t>10750; 21951</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11901; 45530</t>
+          <t>13745; 32920</t>
         </is>
       </c>
     </row>
@@ -2185,32 +2185,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3389</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6245</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4013</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>4226</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>5072</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>6627</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3389</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>6245</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>6266</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11246</t>
+          <t>10279</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1472; 8057</t>
+          <t>1279; 7641</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2275; 8934</t>
+          <t>3230; 10209</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3423; 11024</t>
+          <t>1725; 7732</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1262; 6904</t>
+          <t>1956; 8233</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3293; 10640</t>
+          <t>2395; 8958</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1777; 8549</t>
+          <t>3338; 10590</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4127; 12842</t>
+          <t>4161; 12712</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7048; 17109</t>
+          <t>6821; 16798</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6670; 16879</t>
+          <t>6231; 15463</t>
         </is>
       </c>
     </row>
@@ -2348,32 +2348,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2401,32 +2401,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2679</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2234</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3490</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>1339</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1206</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>5038</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2679</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2234</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4241</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9279</t>
+          <t>8611</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4065</t>
+          <t>742; 6101</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3865</t>
+          <t>637; 5043</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2538; 7941</t>
+          <t>1237; 7096</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>692; 5990</t>
+          <t>0; 4108</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>653; 5040</t>
+          <t>0; 3809</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1410; 7872</t>
+          <t>2586; 7950</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1900; 8227</t>
+          <t>1398; 7508</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1206; 7109</t>
+          <t>1252; 7364</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5520; 14118</t>
+          <t>4922; 12833</t>
         </is>
       </c>
     </row>
@@ -2511,32 +2511,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>41</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>22618</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>23042</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>30293</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>16864</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>21104</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>31464</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>22618</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>23042</t>
-        </is>
-      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33516</t>
+          <t>26567</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>64980</t>
+          <t>56860</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11519; 24149</t>
+          <t>16194; 30943</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>15108; 28145</t>
+          <t>16713; 30507</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18614; 47558</t>
+          <t>22247; 44815</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16456; 31428</t>
+          <t>10781; 23382</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>15819; 30417</t>
+          <t>15160; 28851</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24664; 48262</t>
+          <t>19201; 34520</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30011; 49638</t>
+          <t>30659; 49530</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>35094; 54222</t>
+          <t>35318; 53970</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>48145; 85329</t>
+          <t>45871; 72825</t>
         </is>
       </c>
     </row>
